--- a/SohamC-Bill-2025.xlsx
+++ b/SohamC-Bill-2025.xlsx
@@ -8,34 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383E2348-9707-4FFC-A0B3-0BE2C2C25DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19049C8A-FD89-4621-97EB-E02A823243BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Muktangan (2)" sheetId="18" r:id="rId1"/>
-    <sheet name="Navanand (2)" sheetId="36" r:id="rId2"/>
-    <sheet name="Prathamesh" sheetId="19" r:id="rId3"/>
-    <sheet name="Shanti" sheetId="20" r:id="rId4"/>
-    <sheet name="THAKKAR" sheetId="35" r:id="rId5"/>
-    <sheet name="Daivadnya" sheetId="42" r:id="rId6"/>
-    <sheet name="Hanuman" sheetId="41" r:id="rId7"/>
-    <sheet name="Sai-Kiran" sheetId="27" r:id="rId8"/>
-    <sheet name="Surendra" sheetId="28" r:id="rId9"/>
+    <sheet name="Surendra" sheetId="28" r:id="rId2"/>
+    <sheet name="Navanand (2)" sheetId="36" r:id="rId3"/>
+    <sheet name="Prathamesh" sheetId="19" r:id="rId4"/>
+    <sheet name="Shanti" sheetId="20" r:id="rId5"/>
+    <sheet name="THAKKAR" sheetId="35" r:id="rId6"/>
+    <sheet name="Daivadnya" sheetId="42" r:id="rId7"/>
+    <sheet name="Hanuman" sheetId="41" r:id="rId8"/>
+    <sheet name="Sai-Kiran" sheetId="27" r:id="rId9"/>
     <sheet name="AARTI" sheetId="39" r:id="rId10"/>
     <sheet name="Sheet1" sheetId="46" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="9">AARTI!$A$1:$J$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">Daivadnya!$A$1:$J$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">Hanuman!$A$1:$J$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Daivadnya!$A$1:$J$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">Hanuman!$A$1:$J$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Muktangan (2)'!$A$1:$J$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Navanand (2)'!$A$1:$J$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Prathamesh!$A$1:$J$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Sai-Kiran'!$A$1:$J$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">Shanti!$A$1:$J$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">Surendra!$A$1:$J$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">THAKKAR!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Navanand (2)'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">Prathamesh!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Sai-Kiran'!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">Shanti!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Surendra!$A$1:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">THAKKAR!$A$1:$J$36</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="64">
   <si>
     <t>SOHAM CONSULTANCY</t>
   </si>
@@ -96,9 +96,6 @@
     </r>
   </si>
   <si>
-    <t>Total  Amount :- Rs. Five Thousand Only.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">437/29, Gajanan Vijay CHS, Sector 4, Chatkop, Kandivali-West, Mumbai - 400 067 </t>
     </r>
@@ -204,12 +201,6 @@
     <t>CTS. No.1313,1314, 1287, I. C. Colony Road, Borivali-West, Mumbai - 400 103</t>
   </si>
   <si>
-    <t>SC/2020-21/ACCT/010</t>
-  </si>
-  <si>
-    <t>Professional Charges towards account writing charges for the year 2019-2020.</t>
-  </si>
-  <si>
     <t>SC/2022-23/007</t>
   </si>
   <si>
@@ -219,9 +210,6 @@
     <t>Total  Amount :- Rs. Eighteen Thousand Only.</t>
   </si>
   <si>
-    <t>SC/2023-24/004</t>
-  </si>
-  <si>
     <t xml:space="preserve">Filling Income Tax Return </t>
   </si>
   <si>
@@ -234,9 +222,6 @@
     <t>Note : Please draw A cheque in favour of " JYOTI  B. BORIDKAR"</t>
   </si>
   <si>
-    <t>Total  Amount :- Rs. Four Thousand Only.</t>
-  </si>
-  <si>
     <t>SC/2024-25/001</t>
   </si>
   <si>
@@ -283,6 +268,27 @@
   </si>
   <si>
     <t>Professional Charges towards account writing charges for the year 2025-2026</t>
+  </si>
+  <si>
+    <t>SC/2026-27/003</t>
+  </si>
+  <si>
+    <t>Professional Charges towards account writing charges for the year 2020-2021 To 2024-2025</t>
+  </si>
+  <si>
+    <t>Out of Pocket Expenses : Typing, Xerox, Conveyance</t>
+  </si>
+  <si>
+    <t>Total  Amount :- Rs. Twenty One  Thousand Only.</t>
+  </si>
+  <si>
+    <t>SC/2026-27/004</t>
+  </si>
+  <si>
+    <t>Professional Charges towards account writing charges for the year 2024-2025 &amp; 2025-2026</t>
+  </si>
+  <si>
+    <t>Total  Amount :- Rs. Three  Thousand Only.</t>
   </si>
 </sst>
 </file>
@@ -734,6 +740,132 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -743,129 +875,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -877,9 +886,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1061,7 +1067,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1110,7 +1116,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1159,7 +1165,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1208,7 +1214,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1257,7 +1263,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1306,7 +1312,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1355,7 +1361,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1404,7 +1410,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="soham1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1730,77 +1736,77 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="32">
+        <v>55</v>
+      </c>
+      <c r="I6" s="30">
         <v>46268</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -1831,12 +1837,12 @@
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="L12" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -1865,52 +1871,52 @@
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="40">
+      <c r="A17" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="38">
         <v>7500</v>
       </c>
-      <c r="I17" s="41"/>
+      <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="57"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
+      <c r="A18" s="58"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="53"/>
       <c r="G18" s="59"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="57"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
+      <c r="A19" s="58"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
       <c r="G19" s="59"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="46"/>
@@ -1925,7 +1931,7 @@
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="51" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B22" s="51"/>
       <c r="C22" s="51"/>
@@ -1972,18 +1978,18 @@
       <c r="D27" s="2"/>
     </row>
     <row r="34" spans="1:10" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A34" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
+      <c r="A34" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2020,77 +2026,77 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="32">
+        <v>30</v>
+      </c>
+      <c r="I6" s="30">
         <v>44126</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -2114,7 +2120,7 @@
     </row>
     <row r="12" spans="1:12" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2123,7 +2129,7 @@
     </row>
     <row r="13" spans="1:12" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2131,7 +2137,7 @@
     </row>
     <row r="14" spans="1:12" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2150,52 +2156,52 @@
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="40">
+      <c r="A17" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="38">
         <v>7500</v>
       </c>
-      <c r="I17" s="41"/>
+      <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="75"/>
@@ -2210,7 +2216,7 @@
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="51"/>
       <c r="C22" s="51"/>
@@ -2257,18 +2263,18 @@
       <c r="D27" s="2"/>
     </row>
     <row r="34" spans="1:10" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="70"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="70"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2302,6 +2308,319 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:P35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="7"/>
+      <c r="C1" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+    </row>
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+    </row>
+    <row r="4" spans="1:16" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="30">
+        <v>46272</v>
+      </c>
+      <c r="J6" s="30"/>
+    </row>
+    <row r="8" spans="1:16" ht="25.2" x14ac:dyDescent="0.6">
+      <c r="A8" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+    </row>
+    <row r="9" spans="1:16" ht="25.2" x14ac:dyDescent="0.6">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" ht="19.8" x14ac:dyDescent="0.45">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" ht="19.8" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" ht="19.8" x14ac:dyDescent="0.45">
+      <c r="A12" s="4" t="str">
+        <f>PROPER(L12)</f>
+        <v>Dahisar  "Surendra" Co-Op. Hsg. Soct. Ltd.</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="L12" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+    </row>
+    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="53"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="53"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+    </row>
+    <row r="17" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="38">
+        <v>20000</v>
+      </c>
+      <c r="I18" s="39"/>
+    </row>
+    <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
+    </row>
+    <row r="20" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
+    </row>
+    <row r="21" spans="1:9" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="40">
+        <v>1000</v>
+      </c>
+      <c r="I21" s="41"/>
+    </row>
+    <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="46"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="50"/>
+    </row>
+    <row r="23" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="52">
+        <f>SUM(H18:H22)</f>
+        <v>21000</v>
+      </c>
+      <c r="I23" s="52"/>
+    </row>
+    <row r="24" spans="1:9" ht="20.399999999999999" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="18.600000000000001" x14ac:dyDescent="0.45">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" ht="18.600000000000001" x14ac:dyDescent="0.45">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="35" spans="1:10" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
+      <c r="A35" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="L12:P12"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="A13:G16"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="C1:J3"/>
+    <mergeCell ref="C4:J4"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A18:G20"/>
+    <mergeCell ref="H18:I20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.26" top="0.31" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2313,77 +2632,77 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="C4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="32">
+        <v>41</v>
+      </c>
+      <c r="I6" s="30">
         <v>45966</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -2407,7 +2726,7 @@
     </row>
     <row r="12" spans="1:12" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2422,46 +2741,46 @@
       <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="L13" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
+      <c r="A14" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="44"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
+      <c r="A15" s="62"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="45"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A18" s="3"/>
@@ -2473,57 +2792,57 @@
       <c r="A19" s="17">
         <v>1</v>
       </c>
-      <c r="B19" s="55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="40">
+      <c r="B19" s="56" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="38">
         <v>12000</v>
       </c>
-      <c r="I19" s="41"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
       <c r="G20" s="59"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
       <c r="G21" s="59"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
     </row>
     <row r="22" spans="1:10" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
         <v>2</v>
       </c>
-      <c r="B22" s="62" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="42">
+      <c r="B22" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="65"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="40">
         <v>3000</v>
       </c>
-      <c r="I22" s="43"/>
+      <c r="I22" s="41"/>
     </row>
     <row r="23" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20"/>
@@ -2538,7 +2857,7 @@
     </row>
     <row r="24" spans="1:10" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="51" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B24" s="51"/>
       <c r="C24" s="51"/>
@@ -2585,18 +2904,18 @@
       <c r="D29" s="2"/>
     </row>
     <row r="31" spans="1:10" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="65"/>
-      <c r="C31" s="65"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2621,7 +2940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2633,77 +2952,77 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="C4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="32">
+        <v>52</v>
+      </c>
+      <c r="I6" s="30">
         <v>46134</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -2734,46 +3053,46 @@
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="L12" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="62" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="44"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
+      <c r="A14" s="62"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
     </row>
     <row r="16" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
     </row>
     <row r="17" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A17" s="3"/>
@@ -2782,56 +3101,56 @@
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="40">
+      <c r="A18" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="38">
         <v>4000</v>
       </c>
-      <c r="I18" s="41"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="42">
+      <c r="A21" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="40">
         <v>2000</v>
       </c>
-      <c r="I21" s="43"/>
+      <c r="I21" s="41"/>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="46"/>
@@ -2846,7 +3165,7 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="51"/>
       <c r="C23" s="51"/>
@@ -2893,18 +3212,18 @@
       <c r="D28" s="2"/>
     </row>
     <row r="35" spans="1:10" s="9" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="26" t="s">
+      <c r="A35" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="28"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2929,7 +3248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2941,77 +3260,77 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="C4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="32">
-        <v>45555</v>
-      </c>
-      <c r="J6" s="32"/>
+        <v>61</v>
+      </c>
+      <c r="I6" s="30">
+        <v>46285</v>
+      </c>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -3042,46 +3361,46 @@
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="L12" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
+      <c r="A13" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="63"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="44"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
+      <c r="A14" s="62"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
+      <c r="F14" s="63"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
     </row>
     <row r="17" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A17" s="3"/>
@@ -3090,50 +3409,50 @@
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="40">
-        <v>4000</v>
-      </c>
-      <c r="I18" s="41"/>
+      <c r="A18" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="38">
+        <v>3000</v>
+      </c>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="67"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="69"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="45"/>
       <c r="H21" s="11"/>
       <c r="I21" s="12"/>
     </row>
@@ -3150,7 +3469,7 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="51" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B23" s="51"/>
       <c r="C23" s="51"/>
@@ -3160,7 +3479,7 @@
       <c r="G23" s="51"/>
       <c r="H23" s="52">
         <f>SUM(H18:H22)</f>
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I23" s="52"/>
     </row>
@@ -3197,18 +3516,18 @@
       <c r="D28" s="2"/>
     </row>
     <row r="35" spans="1:10" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A35" s="66" t="s">
+      <c r="A35" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3232,7 +3551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3244,77 +3563,77 @@
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:16" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="32">
+        <v>44</v>
+      </c>
+      <c r="I6" s="30">
         <v>45931</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:16" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:16" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -3344,51 +3663,51 @@
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
-      <c r="L12" s="74" t="s">
+      <c r="L12" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+    </row>
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-    </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
     </row>
     <row r="17" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A17" s="3"/>
@@ -3397,56 +3716,56 @@
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="71" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="40">
+      <c r="A18" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="38">
         <v>12000</v>
       </c>
-      <c r="I18" s="41"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="62"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="62" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="63"/>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="63"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="42">
+      <c r="A21" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="65"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="40">
         <v>3000</v>
       </c>
-      <c r="I21" s="43"/>
+      <c r="I21" s="41"/>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="46"/>
@@ -3461,7 +3780,7 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="51" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B23" s="51"/>
       <c r="C23" s="51"/>
@@ -3508,18 +3827,18 @@
       <c r="D28" s="2"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="18" x14ac:dyDescent="0.35">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="70"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -3546,7 +3865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3558,77 +3877,77 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="32">
+        <v>49</v>
+      </c>
+      <c r="I6" s="30">
         <v>45966</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -3652,7 +3971,7 @@
     </row>
     <row r="12" spans="1:12" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3661,7 +3980,7 @@
     </row>
     <row r="13" spans="1:12" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -3692,56 +4011,56 @@
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="35"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="40">
+      <c r="A17" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="38">
         <v>6000</v>
       </c>
-      <c r="I17" s="41"/>
+      <c r="I17" s="39"/>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="43"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="41"/>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="63"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="42">
+      <c r="A20" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="65"/>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="40">
         <v>3000</v>
       </c>
-      <c r="I20" s="43"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="75"/>
@@ -3756,7 +4075,7 @@
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="51" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B22" s="51"/>
       <c r="C22" s="51"/>
@@ -3803,18 +4122,18 @@
       <c r="D27" s="2"/>
     </row>
     <row r="34" spans="1:10" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A34" s="65" t="s">
+      <c r="A34" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="65"/>
-      <c r="C34" s="65"/>
-      <c r="D34" s="65"/>
-      <c r="E34" s="65"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="65"/>
-      <c r="J34" s="65"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3839,7 +4158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:U36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3851,77 +4170,77 @@
   <sheetData>
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:21" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="C4" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="32">
+        <v>34</v>
+      </c>
+      <c r="I6" s="30">
         <v>44880</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:21" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:21" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -3945,7 +4264,7 @@
     </row>
     <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -3970,7 +4289,7 @@
       <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="L13" s="84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M13" s="84"/>
       <c r="N13" s="84"/>
@@ -3983,15 +4302,15 @@
       <c r="U13" s="25"/>
     </row>
     <row r="14" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
+      <c r="A14" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
       <c r="L14" s="80" t="str">
         <f>PROPER(AB14)</f>
         <v/>
@@ -4007,13 +4326,13 @@
       <c r="U14" s="81"/>
     </row>
     <row r="15" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
       <c r="L15" s="82"/>
       <c r="M15" s="83"/>
       <c r="N15" s="83"/>
@@ -4026,13 +4345,13 @@
       <c r="U15" s="25"/>
     </row>
     <row r="16" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
       <c r="L16" s="82"/>
       <c r="M16" s="83"/>
       <c r="N16" s="83"/>
@@ -4045,13 +4364,13 @@
       <c r="U16" s="25"/>
     </row>
     <row r="17" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="58"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
       <c r="L17" s="83"/>
       <c r="M17" s="83"/>
       <c r="N17" s="83"/>
@@ -4070,52 +4389,52 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="35"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="40">
+      <c r="A19" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="38">
         <v>18000</v>
       </c>
-      <c r="I19" s="41"/>
+      <c r="I19" s="39"/>
     </row>
     <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
     </row>
     <row r="22" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="67"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="43"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="41"/>
     </row>
     <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="46"/>
@@ -4130,7 +4449,7 @@
     </row>
     <row r="24" spans="1:21" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="51" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B24" s="51"/>
       <c r="C24" s="51"/>
@@ -4177,18 +4496,18 @@
       <c r="D29" s="2"/>
     </row>
     <row r="36" spans="1:10" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A36" s="66" t="s">
+      <c r="A36" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="66"/>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
-      <c r="G36" s="66"/>
-      <c r="H36" s="66"/>
-      <c r="I36" s="66"/>
-      <c r="J36" s="66"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4216,7 +4535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4228,77 +4547,77 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
     </row>
     <row r="4" spans="1:12" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="32">
+        <v>50</v>
+      </c>
+      <c r="I6" s="30">
         <v>46031</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="25.2" x14ac:dyDescent="0.6">
       <c r="A9" s="1"/>
@@ -4329,12 +4648,12 @@
       <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="L12" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="61"/>
       <c r="C13" s="61"/>
@@ -4373,52 +4692,52 @@
       <c r="D17" s="2"/>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="40">
+      <c r="A18" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="38">
         <v>6000</v>
       </c>
-      <c r="I18" s="41"/>
+      <c r="I18" s="39"/>
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="41"/>
     </row>
     <row r="21" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
+      <c r="A21" s="35"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="41"/>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="46"/>
@@ -4433,7 +4752,7 @@
     </row>
     <row r="23" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="51"/>
       <c r="C23" s="51"/>
@@ -4480,18 +4799,18 @@
       <c r="D28" s="2"/>
     </row>
     <row r="35" spans="1:10" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A35" s="65" t="s">
+      <c r="A35" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="65"/>
-      <c r="C35" s="65"/>
-      <c r="D35" s="65"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4514,313 +4833,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="8.44140625" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="7"/>
-      <c r="C1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-    </row>
-    <row r="4" spans="1:16" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="32">
-        <v>44286</v>
-      </c>
-      <c r="J6" s="32"/>
-    </row>
-    <row r="8" spans="1:16" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A8" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-    </row>
-    <row r="9" spans="1:16" ht="25.2" x14ac:dyDescent="0.6">
-      <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" ht="19.8" x14ac:dyDescent="0.45">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" ht="19.8" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" ht="19.8" x14ac:dyDescent="0.45">
-      <c r="A12" s="4" t="str">
-        <f>PROPER(L12)</f>
-        <v>Dahisar  "Surendra" Co-Op. Hsg. Soct. Ltd.</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-      <c r="L12" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="M12" s="74"/>
-      <c r="N12" s="74"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-    </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-    </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-    </row>
-    <row r="17" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="40">
-        <v>5000</v>
-      </c>
-      <c r="I18" s="41"/>
-    </row>
-    <row r="19" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="43"/>
-    </row>
-    <row r="20" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="43"/>
-    </row>
-    <row r="21" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="67"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="43"/>
-    </row>
-    <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="48"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="50"/>
-    </row>
-    <row r="23" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="52">
-        <f>SUM(H18:H22)</f>
-        <v>5000</v>
-      </c>
-      <c r="I23" s="52"/>
-    </row>
-    <row r="24" spans="1:9" ht="20.399999999999999" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:9" ht="18.600000000000001" x14ac:dyDescent="0.45">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:9" ht="18.600000000000001" x14ac:dyDescent="0.45">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:9" ht="19.8" x14ac:dyDescent="0.45">
-      <c r="A28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="35" spans="1:10" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A35" s="66" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" s="66"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
-      <c r="F35" s="66"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="66"/>
-      <c r="I35" s="66"/>
-      <c r="J35" s="66"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="L12:P12"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="A13:G16"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="C1:J3"/>
-    <mergeCell ref="C4:J4"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A18:G20"/>
-    <mergeCell ref="H18:I20"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.26" top="0.31" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>